--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2631,7 +2631,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E57" s="3" t="n"/>
@@ -2642,7 +2642,7 @@
       <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
@@ -2675,7 +2675,7 @@
       <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E59" s="3" t="n"/>
@@ -2708,7 +2708,7 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
@@ -2741,7 +2741,7 @@
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="n"/>
@@ -2774,7 +2774,7 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:16</t>
+          <t>2026-09-13 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2778,6 +2778,171 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n"/>
+      <c r="F63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n"/>
+      <c r="F65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>S38/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 16:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -2807,40 +2807,40 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>S38/2026</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:07</t>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -2873,40 +2873,40 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>S38/2026</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>14/09/2026</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:07</t>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -2939,7 +2939,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 16:07</t>
+          <t>2026-09-15 14:34</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -2807,7 +2807,7 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -2840,7 +2840,7 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -2873,7 +2873,7 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -2939,7 +2939,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:34</t>
+          <t>2026-09-16 14:31</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -2807,7 +2807,7 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -2840,7 +2840,7 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -2873,7 +2873,7 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -2939,7 +2939,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:31</t>
+          <t>2026-09-17 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -2807,7 +2807,7 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -2840,7 +2840,7 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -2873,7 +2873,7 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -2939,7 +2939,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:35</t>
+          <t>2026-09-18 14:00</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -2807,7 +2807,7 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -2840,7 +2840,7 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -2873,7 +2873,7 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -2939,7 +2939,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00</t>
+          <t>2026-09-19 13:37</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E62" s="2" t="n"/>
@@ -2807,7 +2807,7 @@
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -2840,7 +2840,7 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -2873,7 +2873,7 @@
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E65" s="2" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>20/09/2026</t>
         </is>
       </c>
       <c r="E66" s="2" t="n"/>
@@ -2939,7 +2939,7 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:37</t>
+          <t>2026-09-20 13:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2943,6 +2943,171 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>S39/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21 16:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
@@ -2972,40 +2972,40 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>S39/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 16:09</t>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
@@ -3038,40 +3038,40 @@
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>S39/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-21 16:09</t>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -3104,7 +3104,7 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:09</t>
+          <t>2026-09-22 14:19</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
@@ -2972,7 +2972,7 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n"/>
@@ -3005,7 +3005,7 @@
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
@@ -3038,7 +3038,7 @@
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n"/>
@@ -3071,7 +3071,7 @@
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -3104,7 +3104,7 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:19</t>
+          <t>2026-09-23 14:34</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
@@ -2972,7 +2972,7 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n"/>
@@ -3005,7 +3005,7 @@
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
@@ -3038,7 +3038,7 @@
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n"/>
@@ -3071,7 +3071,7 @@
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -3104,7 +3104,7 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23 14:34</t>
+          <t>2026-09-24 14:32</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
@@ -2972,7 +2972,7 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n"/>
@@ -3005,7 +3005,7 @@
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
@@ -3038,7 +3038,7 @@
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n"/>
@@ -3071,7 +3071,7 @@
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -3104,7 +3104,7 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 14:32</t>
+          <t>2026-09-25 14:54</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
@@ -2972,7 +2972,7 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n"/>
@@ -3005,7 +3005,7 @@
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
@@ -3038,7 +3038,7 @@
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n"/>
@@ -3071,7 +3071,7 @@
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -3104,7 +3104,7 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25 14:54</t>
+          <t>2026-09-26 13:59</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
@@ -2972,7 +2972,7 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E68" s="3" t="n"/>
@@ -3005,7 +3005,7 @@
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E69" s="3" t="n"/>
@@ -3038,7 +3038,7 @@
       <c r="H69" s="3" t="inlineStr"/>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E70" s="3" t="n"/>
@@ -3071,7 +3071,7 @@
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -3104,7 +3104,7 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:59</t>
+          <t>2026-09-27 14:55</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3108,6 +3108,171 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n"/>
+      <c r="F75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>S40/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28 17:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -3137,40 +3137,40 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>S40/2026</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:55</t>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -3203,40 +3203,40 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>S40/2026</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28 17:55</t>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28 17:55</t>
+          <t>2026-09-29 16:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -3137,7 +3137,7 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -3170,7 +3170,7 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -3203,7 +3203,7 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -3236,7 +3236,7 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29 16:17</t>
+          <t>2026-09-30 16:13</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3121,12 +3121,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -3137,7 +3137,7 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -3170,7 +3170,7 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -3203,7 +3203,7 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -3236,7 +3236,7 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>
@@ -3253,12 +3253,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30 16:13</t>
+          <t>2026-10-01 16:57</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -3137,7 +3137,7 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -3170,7 +3170,7 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -3203,7 +3203,7 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -3236,7 +3236,7 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01 16:57</t>
+          <t>2026-10-02 16:04</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -3137,7 +3137,7 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -3170,7 +3170,7 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -3203,7 +3203,7 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -3236,7 +3236,7 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 16:04</t>
+          <t>2026-10-03 14:32</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E72" s="2" t="n"/>
@@ -3137,7 +3137,7 @@
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E73" s="2" t="n"/>
@@ -3170,7 +3170,7 @@
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E74" s="2" t="n"/>
@@ -3203,7 +3203,7 @@
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E75" s="2" t="n"/>
@@ -3236,7 +3236,7 @@
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/10/2026</t>
         </is>
       </c>
       <c r="E76" s="2" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:32</t>
+          <t>2026-10-04 15:06</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3273,6 +3273,171 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>S41/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n"/>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 19:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
@@ -3302,40 +3302,40 @@
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>S41/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:00</t>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -3368,40 +3368,40 @@
       <c r="H79" s="3" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>S41/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05 19:00</t>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3434,7 +3434,7 @@
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:00</t>
+          <t>2026-10-06 16:24</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
@@ -3302,7 +3302,7 @@
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n"/>
@@ -3335,7 +3335,7 @@
       <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -3368,7 +3368,7 @@
       <c r="H79" s="3" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
@@ -3401,7 +3401,7 @@
       <c r="H80" s="3" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3434,7 +3434,7 @@
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06 16:24</t>
+          <t>2026-10-07 17:10</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
@@ -3302,7 +3302,7 @@
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n"/>
@@ -3335,7 +3335,7 @@
       <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -3368,7 +3368,7 @@
       <c r="H79" s="3" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
@@ -3401,7 +3401,7 @@
       <c r="H80" s="3" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3434,7 +3434,7 @@
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07 17:10</t>
+          <t>2026-10-08 17:08</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
@@ -3302,7 +3302,7 @@
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n"/>
@@ -3335,7 +3335,7 @@
       <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -3368,7 +3368,7 @@
       <c r="H79" s="3" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
@@ -3401,7 +3401,7 @@
       <c r="H80" s="3" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3434,7 +3434,7 @@
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08 17:08</t>
+          <t>2026-10-09 16:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
@@ -3302,7 +3302,7 @@
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n"/>
@@ -3335,7 +3335,7 @@
       <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -3368,7 +3368,7 @@
       <c r="H79" s="3" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
@@ -3401,7 +3401,7 @@
       <c r="H80" s="3" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3434,7 +3434,7 @@
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 16:45</t>
+          <t>2026-10-10 15:43</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
@@ -3302,7 +3302,7 @@
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E78" s="3" t="n"/>
@@ -3335,7 +3335,7 @@
       <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
@@ -3368,7 +3368,7 @@
       <c r="H79" s="3" t="inlineStr"/>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E80" s="3" t="n"/>
@@ -3401,7 +3401,7 @@
       <c r="H80" s="3" t="inlineStr"/>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
@@ -3434,7 +3434,7 @@
       <c r="H81" s="3" t="inlineStr"/>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-10-10 15:43</t>
+          <t>2026-10-11 16:05</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3438,6 +3438,171 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n"/>
+      <c r="F85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>S42/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>12/10/2026</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12 19:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -3467,40 +3467,40 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>S42/2026</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:34</t>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -3533,40 +3533,40 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>S42/2026</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>12/10/2026</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="3" t="inlineStr"/>
-      <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12 19:34</t>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -3599,7 +3599,7 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12 19:34</t>
+          <t>2026-10-13 17:17</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -3467,7 +3467,7 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
@@ -3500,7 +3500,7 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -3533,7 +3533,7 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -3599,7 +3599,7 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 17:17</t>
+          <t>2026-10-14 14:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -3467,7 +3467,7 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
@@ -3500,7 +3500,7 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -3533,7 +3533,7 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -3599,7 +3599,7 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:50</t>
+          <t>2026-10-15 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -3467,7 +3467,7 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
@@ -3500,7 +3500,7 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -3533,7 +3533,7 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -3599,7 +3599,7 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:35</t>
+          <t>2026-10-16 14:26</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -3467,7 +3467,7 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
@@ -3500,7 +3500,7 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -3533,7 +3533,7 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -3599,7 +3599,7 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:26</t>
+          <t>2026-10-17 13:25</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E82" s="2" t="n"/>
@@ -3467,7 +3467,7 @@
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E83" s="2" t="n"/>
@@ -3500,7 +3500,7 @@
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E84" s="2" t="n"/>
@@ -3533,7 +3533,7 @@
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E85" s="2" t="n"/>
@@ -3566,7 +3566,7 @@
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -3599,7 +3599,7 @@
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:25</t>
+          <t>2026-10-18 13:44</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3603,6 +3603,171 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
+      <c r="F87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>S43/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr"/>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 16:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n"/>
@@ -3632,40 +3632,40 @@
       <c r="H87" s="3" t="inlineStr"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>S43/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19 16:47</t>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -3698,40 +3698,40 @@
       <c r="H89" s="3" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>S43/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>19/10/2026</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19 16:47</t>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>19/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
@@ -3764,7 +3764,7 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-19 16:47</t>
+          <t>2026-10-20 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n"/>
@@ -3632,7 +3632,7 @@
       <c r="H87" s="3" t="inlineStr"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n"/>
@@ -3665,7 +3665,7 @@
       <c r="H88" s="3" t="inlineStr"/>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -3698,7 +3698,7 @@
       <c r="H89" s="3" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
@@ -3731,7 +3731,7 @@
       <c r="H90" s="3" t="inlineStr"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
@@ -3764,7 +3764,7 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:35</t>
+          <t>2026-10-21 14:50</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n"/>
@@ -3632,7 +3632,7 @@
       <c r="H87" s="3" t="inlineStr"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n"/>
@@ -3665,7 +3665,7 @@
       <c r="H88" s="3" t="inlineStr"/>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -3698,7 +3698,7 @@
       <c r="H89" s="3" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
@@ -3731,7 +3731,7 @@
       <c r="H90" s="3" t="inlineStr"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
@@ -3764,7 +3764,7 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-21 14:50</t>
+          <t>2026-10-22 14:49</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n"/>
@@ -3632,7 +3632,7 @@
       <c r="H87" s="3" t="inlineStr"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n"/>
@@ -3665,7 +3665,7 @@
       <c r="H88" s="3" t="inlineStr"/>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -3698,7 +3698,7 @@
       <c r="H89" s="3" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
@@ -3731,7 +3731,7 @@
       <c r="H90" s="3" t="inlineStr"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
@@ -3764,7 +3764,7 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:49</t>
+          <t>2026-10-23 14:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n"/>
@@ -3632,7 +3632,7 @@
       <c r="H87" s="3" t="inlineStr"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n"/>
@@ -3665,7 +3665,7 @@
       <c r="H88" s="3" t="inlineStr"/>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -3698,7 +3698,7 @@
       <c r="H89" s="3" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
@@ -3731,7 +3731,7 @@
       <c r="H90" s="3" t="inlineStr"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>23/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
@@ -3764,7 +3764,7 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:35</t>
+          <t>2026-10-24 13:45</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E87" s="3" t="n"/>
@@ -3632,7 +3632,7 @@
       <c r="H87" s="3" t="inlineStr"/>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E88" s="3" t="n"/>
@@ -3665,7 +3665,7 @@
       <c r="H88" s="3" t="inlineStr"/>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -3698,7 +3698,7 @@
       <c r="H89" s="3" t="inlineStr"/>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
@@ -3731,7 +3731,7 @@
       <c r="H90" s="3" t="inlineStr"/>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>24/10/2026</t>
+          <t>25/10/2026</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
@@ -3764,7 +3764,7 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:45</t>
+          <t>2026-10-25 14:03</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3768,6 +3768,171 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Academias</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>S44/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>26/10/2026</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
@@ -3797,40 +3797,40 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>S44/2026</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26 16:26</t>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
@@ -3863,40 +3863,40 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>S44/2026</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>26/10/2026</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26 16:26</t>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>26/10/2026</t>
+          <t>28/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
@@ -3929,7 +3929,7 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26 16:26</t>
+          <t>2026-10-28 16:23</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
@@ -3797,7 +3797,7 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n"/>
@@ -3830,7 +3830,7 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
@@ -3863,7 +3863,7 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n"/>
@@ -3896,7 +3896,7 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>28/10/2026</t>
+          <t>29/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
@@ -3929,7 +3929,7 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28 16:23</t>
+          <t>2026-10-29 16:35</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
@@ -3797,7 +3797,7 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n"/>
@@ -3830,7 +3830,7 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
@@ -3863,7 +3863,7 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n"/>
@@ -3896,7 +3896,7 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>29/10/2026</t>
+          <t>30/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
@@ -3929,7 +3929,7 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29 16:35</t>
+          <t>2026-10-30 16:27</t>
         </is>
       </c>
     </row>

--- a/instagram-metrics/base_seguidores.xlsx
+++ b/instagram-metrics/base_seguidores.xlsx
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E92" s="2" t="n"/>
@@ -3797,7 +3797,7 @@
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E93" s="2" t="n"/>
@@ -3830,7 +3830,7 @@
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E94" s="2" t="n"/>
@@ -3863,7 +3863,7 @@
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E95" s="2" t="n"/>
@@ -3896,7 +3896,7 @@
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>30/10/2026</t>
+          <t>31/10/2026</t>
         </is>
       </c>
       <c r="E96" s="2" t="n"/>
@@ -3929,7 +3929,7 @@
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30 16:27</t>
+          <t>2026-10-31 15:38</t>
         </is>
       </c>
     </row>
